--- a/Codes/Trial 2/Trial2_LSTM_Followers_Results.xlsx
+++ b/Codes/Trial 2/Trial2_LSTM_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,13 +470,13 @@
         <v>2023</v>
       </c>
       <c r="C2" t="n">
-        <v>5.9</v>
+        <v>6.390000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>6.319511890411377</v>
+        <v>0.8625812530517578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4195118904113766</v>
+        <v>5.527418746948244</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,13 +494,13 @@
         <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>4.96</v>
+        <v>8.919999999999998</v>
       </c>
       <c r="D3" t="n">
-        <v>5.785199165344238</v>
+        <v>1.374776363372803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8251991653442383</v>
+        <v>7.545223636627195</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>2023</v>
       </c>
       <c r="C4" t="n">
-        <v>3.87</v>
+        <v>7.390000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>5.504883289337158</v>
+        <v>2.297397375106812</v>
       </c>
       <c r="E4" t="n">
-        <v>1.634883289337159</v>
+        <v>5.092602624893189</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -542,13 +542,13 @@
         <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>3.76</v>
+        <v>6.200000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>4.652605056762695</v>
+        <v>1.824608087539673</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8926050567626955</v>
+        <v>4.375391912460328</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -566,13 +566,13 @@
         <v>2023</v>
       </c>
       <c r="C6" t="n">
-        <v>6.390000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3.808052539825439</v>
+        <v>1.07709002494812</v>
       </c>
       <c r="E6" t="n">
-        <v>2.581947460174562</v>
+        <v>4.42290997505188</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         <v>2024</v>
       </c>
       <c r="C7" t="n">
-        <v>8.919999999999998</v>
+        <v>6.920000000000002</v>
       </c>
       <c r="D7" t="n">
-        <v>4.016441345214844</v>
+        <v>1.872199535369873</v>
       </c>
       <c r="E7" t="n">
-        <v>4.903558654785154</v>
+        <v>5.047800464630129</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>2023</v>
       </c>
       <c r="C8" t="n">
-        <v>7.390000000000001</v>
+        <v>19.77</v>
       </c>
       <c r="D8" t="n">
-        <v>4.604192733764648</v>
+        <v>1.471522450447083</v>
       </c>
       <c r="E8" t="n">
-        <v>2.785807266235352</v>
+        <v>18.29847754955291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         <v>2024</v>
       </c>
       <c r="C9" t="n">
-        <v>6.200000000000001</v>
+        <v>15.39</v>
       </c>
       <c r="D9" t="n">
-        <v>4.89298152923584</v>
+        <v>1.079110980033875</v>
       </c>
       <c r="E9" t="n">
-        <v>1.307018470764161</v>
+        <v>14.31088901996613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -662,13 +662,13 @@
         <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>5.5</v>
+        <v>10.48</v>
       </c>
       <c r="D10" t="n">
-        <v>5.528183937072754</v>
+        <v>0.8210837841033936</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02818393707275391</v>
+        <v>9.658916215896605</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -686,13 +686,13 @@
         <v>2024</v>
       </c>
       <c r="C11" t="n">
-        <v>6.920000000000002</v>
+        <v>8.520000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>6.347836971282959</v>
+        <v>1.157252788543701</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5721630287170427</v>
+        <v>7.3627472114563</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         <v>2023</v>
       </c>
       <c r="C12" t="n">
-        <v>19.77</v>
+        <v>8.4</v>
       </c>
       <c r="D12" t="n">
-        <v>6.469618320465088</v>
+        <v>1.67055332660675</v>
       </c>
       <c r="E12" t="n">
-        <v>13.30038167953491</v>
+        <v>6.72944667339325</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -734,13 +734,13 @@
         <v>2024</v>
       </c>
       <c r="C13" t="n">
-        <v>15.39</v>
+        <v>7.649999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>6.128816604614258</v>
+        <v>2.81489086151123</v>
       </c>
       <c r="E13" t="n">
-        <v>9.261183395385745</v>
+        <v>4.835109138488769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>2023</v>
       </c>
       <c r="C14" t="n">
-        <v>10.48</v>
+        <v>24.15</v>
       </c>
       <c r="D14" t="n">
-        <v>4.93562126159668</v>
+        <v>1.408288240432739</v>
       </c>
       <c r="E14" t="n">
-        <v>5.544378738403319</v>
+        <v>22.74171175956726</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -782,13 +782,13 @@
         <v>2024</v>
       </c>
       <c r="C15" t="n">
-        <v>8.520000000000001</v>
+        <v>28.37</v>
       </c>
       <c r="D15" t="n">
-        <v>4.400413990020752</v>
+        <v>3.315093755722046</v>
       </c>
       <c r="E15" t="n">
-        <v>4.119586009979249</v>
+        <v>25.05490624427796</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         <v>2023</v>
       </c>
       <c r="C16" t="n">
-        <v>8.4</v>
+        <v>15.94999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>5.559492111206055</v>
+        <v>1.780694603919983</v>
       </c>
       <c r="E16" t="n">
-        <v>2.840507888793946</v>
+        <v>14.16930539608001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         <v>2024</v>
       </c>
       <c r="C17" t="n">
-        <v>7.649999999999999</v>
+        <v>39.77999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>4.478399276733398</v>
+        <v>1.687521576881409</v>
       </c>
       <c r="E17" t="n">
-        <v>3.171600723266601</v>
+        <v>38.09247842311859</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>2023</v>
       </c>
       <c r="C18" t="n">
-        <v>24.15</v>
+        <v>19.21</v>
       </c>
       <c r="D18" t="n">
-        <v>5.066840171813965</v>
+        <v>1.512611985206604</v>
       </c>
       <c r="E18" t="n">
-        <v>19.08315982818604</v>
+        <v>17.69738801479339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -878,13 +878,13 @@
         <v>2024</v>
       </c>
       <c r="C19" t="n">
-        <v>28.37</v>
+        <v>21.05999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>5.14145565032959</v>
+        <v>2.099493026733398</v>
       </c>
       <c r="E19" t="n">
-        <v>23.22854434967041</v>
+        <v>18.96050697326659</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         <v>2023</v>
       </c>
       <c r="C20" t="n">
-        <v>15.94999999999999</v>
+        <v>3.86</v>
       </c>
       <c r="D20" t="n">
-        <v>3.348320722579956</v>
+        <v>1.184630513191223</v>
       </c>
       <c r="E20" t="n">
-        <v>12.60167927742004</v>
+        <v>2.675369486808777</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -926,13 +926,13 @@
         <v>2024</v>
       </c>
       <c r="C21" t="n">
-        <v>39.77999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="D21" t="n">
-        <v>3.245028495788574</v>
+        <v>1.110615015029907</v>
       </c>
       <c r="E21" t="n">
-        <v>36.53497150421142</v>
+        <v>2.229384984970093</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -950,13 +950,13 @@
         <v>2023</v>
       </c>
       <c r="C22" t="n">
-        <v>19.21</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>6.30698299407959</v>
+        <v>0.9152169823646545</v>
       </c>
       <c r="E22" t="n">
-        <v>12.90301700592041</v>
+        <v>8.944783017635345</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -974,111 +974,15 @@
         <v>2024</v>
       </c>
       <c r="C23" t="n">
-        <v>21.05999999999999</v>
+        <v>6.980000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>6.62960958480835</v>
+        <v>1.475495338439941</v>
       </c>
       <c r="E23" t="n">
-        <v>14.43039041519164</v>
+        <v>5.50450466156006</v>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="D24" t="n">
-        <v>6.499886989593506</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.639886989593506</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C25" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="D25" t="n">
-        <v>5.833693027496338</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.493693027496338</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C26" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="D26" t="n">
-        <v>5.457792282104492</v>
-      </c>
-      <c r="E26" t="n">
-        <v>4.402207717895507</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C27" t="n">
-        <v>6.980000000000001</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4.974894046783447</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.005105953216554</v>
-      </c>
-      <c r="F27" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>
